--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/75.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/75.xlsx
@@ -426,13 +426,13 @@
         <v>0.881729360143138</v>
       </c>
       <c r="E2">
-        <v>-16.74794732161138</v>
+        <v>-29.23956173280975</v>
       </c>
       <c r="F2">
-        <v>-6.072801746783578</v>
+        <v>-6.077085671284841</v>
       </c>
       <c r="G2">
-        <v>-7.355500341097089</v>
+        <v>-16.3797230476875</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.881368379674497</v>
       </c>
       <c r="E3">
-        <v>-18.38466009678165</v>
+        <v>-28.74179639836063</v>
       </c>
       <c r="F3">
-        <v>-5.914021767260492</v>
+        <v>-6.891600272875067</v>
       </c>
       <c r="G3">
-        <v>-8.213338832869656</v>
+        <v>-15.31300402984184</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.7780259670291912</v>
       </c>
       <c r="E4">
-        <v>-19.51455964643548</v>
+        <v>-28.52126424266109</v>
       </c>
       <c r="F4">
-        <v>-5.710425285889343</v>
+        <v>-6.316955748869694</v>
       </c>
       <c r="G4">
-        <v>-6.463606267362039</v>
+        <v>-16.94733759894155</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.5912358499606027</v>
       </c>
       <c r="E5">
-        <v>-19.48279692974568</v>
+        <v>-27.90574047011652</v>
       </c>
       <c r="F5">
-        <v>-5.694119449783979</v>
+        <v>-6.454971364208975</v>
       </c>
       <c r="G5">
-        <v>-7.585967279358992</v>
+        <v>-15.36176836563531</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.3468434028448282</v>
       </c>
       <c r="E6">
-        <v>-20.13429037133319</v>
+        <v>-30.27699890017497</v>
       </c>
       <c r="F6">
-        <v>-6.044158049743983</v>
+        <v>-6.778325707273261</v>
       </c>
       <c r="G6">
-        <v>-7.051092368215564</v>
+        <v>-16.74656956471244</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.07761958970483582</v>
       </c>
       <c r="E7">
-        <v>-20.0717747876573</v>
+        <v>-30.12932309854783</v>
       </c>
       <c r="F7">
-        <v>-5.996447325335454</v>
+        <v>-6.839908111795124</v>
       </c>
       <c r="G7">
-        <v>-6.820158643032624</v>
+        <v>-16.11501844745845</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.1822617615973298</v>
       </c>
       <c r="E8">
-        <v>-19.81285022932073</v>
+        <v>-30.63123877942498</v>
       </c>
       <c r="F8">
-        <v>-6.28428706324601</v>
+        <v>-6.267475233100662</v>
       </c>
       <c r="G8">
-        <v>-7.686601242661758</v>
+        <v>-14.94755621830724</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3989995917012925</v>
       </c>
       <c r="E9">
-        <v>-20.60718079805817</v>
+        <v>-31.04062641514041</v>
       </c>
       <c r="F9">
-        <v>-5.912849033030109</v>
+        <v>-6.772792634731195</v>
       </c>
       <c r="G9">
-        <v>-6.699671338130849</v>
+        <v>-15.48593037608567</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5439321167196604</v>
       </c>
       <c r="E10">
-        <v>-22.16167007067117</v>
+        <v>-32.12222073255442</v>
       </c>
       <c r="F10">
-        <v>-6.06785266579783</v>
+        <v>-5.872487495922178</v>
       </c>
       <c r="G10">
-        <v>-6.829073942169881</v>
+        <v>-15.46502924682349</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.5917915601818547</v>
       </c>
       <c r="E11">
-        <v>-22.26183085877283</v>
+        <v>-32.61566590280022</v>
       </c>
       <c r="F11">
-        <v>-5.580386401319652</v>
+        <v>-6.054468767106451</v>
       </c>
       <c r="G11">
-        <v>-6.572122639593808</v>
+        <v>-15.22175546314291</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5275124875359819</v>
       </c>
       <c r="E12">
-        <v>-22.70485147094322</v>
+        <v>-31.28730597976023</v>
       </c>
       <c r="F12">
-        <v>-5.706740794077073</v>
+        <v>-5.693992753310743</v>
       </c>
       <c r="G12">
-        <v>-6.180375854295232</v>
+        <v>-13.82121593057208</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.3492402055939772</v>
       </c>
       <c r="E13">
-        <v>-22.92371714820793</v>
+        <v>-33.39320941839122</v>
       </c>
       <c r="F13">
-        <v>-5.884126150694741</v>
+        <v>-6.138953934724442</v>
       </c>
       <c r="G13">
-        <v>-5.553610130618253</v>
+        <v>-13.60514324431493</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.06103077609911067</v>
       </c>
       <c r="E14">
-        <v>-24.0798546762622</v>
+        <v>-31.78183345529387</v>
       </c>
       <c r="F14">
-        <v>-5.845849562424486</v>
+        <v>-6.114326911812879</v>
       </c>
       <c r="G14">
-        <v>-4.765859198457595</v>
+        <v>-15.33794567993471</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.3239786101784267</v>
       </c>
       <c r="E15">
-        <v>-25.31748209408451</v>
+        <v>-33.60318570117888</v>
       </c>
       <c r="F15">
-        <v>-5.605746284143584</v>
+        <v>-6.164378749490906</v>
       </c>
       <c r="G15">
-        <v>-5.34871715664722</v>
+        <v>-13.58573351581818</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.7838250205368982</v>
       </c>
       <c r="E16">
-        <v>-25.27917573245362</v>
+        <v>-33.73918030410323</v>
       </c>
       <c r="F16">
-        <v>-5.935371706706531</v>
+        <v>-6.366145258676765</v>
       </c>
       <c r="G16">
-        <v>-5.225693973862364</v>
+        <v>-14.50935751327438</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.29208185831517</v>
       </c>
       <c r="E17">
-        <v>-25.72731352025268</v>
+        <v>-33.59715830227467</v>
       </c>
       <c r="F17">
-        <v>-5.163182833485862</v>
+        <v>-5.582247255770294</v>
       </c>
       <c r="G17">
-        <v>-4.282085868258358</v>
+        <v>-13.94446091990807</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.824450990050786</v>
       </c>
       <c r="E18">
-        <v>-25.95668072874119</v>
+        <v>-34.40109602861939</v>
       </c>
       <c r="F18">
-        <v>-5.602204325863704</v>
+        <v>-5.875716672283758</v>
       </c>
       <c r="G18">
-        <v>-3.810339750003292</v>
+        <v>-14.51759911639439</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.355651506179712</v>
       </c>
       <c r="E19">
-        <v>-27.32381344623484</v>
+        <v>-35.83004241631775</v>
       </c>
       <c r="F19">
-        <v>-4.801823111789338</v>
+        <v>-5.615642070556207</v>
       </c>
       <c r="G19">
-        <v>-3.529579003908781</v>
+        <v>-13.29712512152283</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.859601276359516</v>
       </c>
       <c r="E20">
-        <v>-28.39256953983711</v>
+        <v>-36.09086666950054</v>
       </c>
       <c r="F20">
-        <v>-5.019408467511564</v>
+        <v>-4.89793426453257</v>
       </c>
       <c r="G20">
-        <v>-4.397766261037111</v>
+        <v>-11.6634635931676</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.320131210494206</v>
       </c>
       <c r="E21">
-        <v>-28.74032464430814</v>
+        <v>-36.88634067792491</v>
       </c>
       <c r="F21">
-        <v>-4.460203492475811</v>
+        <v>-5.198099589656513</v>
       </c>
       <c r="G21">
-        <v>-4.288034918592428</v>
+        <v>-13.5556952808676</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.724026888190428</v>
       </c>
       <c r="E22">
-        <v>-28.41206914891414</v>
+        <v>-37.13374026991196</v>
       </c>
       <c r="F22">
-        <v>-4.756324824544679</v>
+        <v>-4.965032716757909</v>
       </c>
       <c r="G22">
-        <v>-3.529777636641137</v>
+        <v>-12.71057921560245</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.059969120015958</v>
       </c>
       <c r="E23">
-        <v>-29.81423640556814</v>
+        <v>-36.50836027368969</v>
       </c>
       <c r="F23">
-        <v>-4.554844174276557</v>
+        <v>-4.615460518190002</v>
       </c>
       <c r="G23">
-        <v>-3.619278235295334</v>
+        <v>-11.7450321247097</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.322369009320544</v>
       </c>
       <c r="E24">
-        <v>-30.99021770672402</v>
+        <v>-38.23669992769416</v>
       </c>
       <c r="F24">
-        <v>-4.075881618711332</v>
+        <v>-5.243707152609338</v>
       </c>
       <c r="G24">
-        <v>-3.679556648474384</v>
+        <v>-11.91910723025566</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.511409092073467</v>
       </c>
       <c r="E25">
-        <v>-30.13705999638994</v>
+        <v>-38.65833934983733</v>
       </c>
       <c r="F25">
-        <v>-3.99407053853156</v>
+        <v>-5.660628820790181</v>
       </c>
       <c r="G25">
-        <v>-2.929585662007889</v>
+        <v>-12.84094849893895</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.628874792395574</v>
       </c>
       <c r="E26">
-        <v>-30.59061836757618</v>
+        <v>-38.03842522174232</v>
       </c>
       <c r="F26">
-        <v>-3.790392496305766</v>
+        <v>-5.046196061218265</v>
       </c>
       <c r="G26">
-        <v>-4.119087848086801</v>
+        <v>-11.31204587362842</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.678902258406754</v>
       </c>
       <c r="E27">
-        <v>-29.68481714690293</v>
+        <v>-37.84916670753975</v>
       </c>
       <c r="F27">
-        <v>-4.048589614670564</v>
+        <v>-4.866627565996163</v>
       </c>
       <c r="G27">
-        <v>-3.062421301771145</v>
+        <v>-11.70469312731368</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.673582081674098</v>
       </c>
       <c r="E28">
-        <v>-29.85135630700901</v>
+        <v>-38.27731128259494</v>
       </c>
       <c r="F28">
-        <v>-4.071790114478794</v>
+        <v>-4.874689420958708</v>
       </c>
       <c r="G28">
-        <v>-4.518660763040216</v>
+        <v>-11.80655530301151</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.626054794019089</v>
       </c>
       <c r="E29">
-        <v>-31.58721775634022</v>
+        <v>-37.46279051249431</v>
       </c>
       <c r="F29">
-        <v>-3.881579115504939</v>
+        <v>-5.046639498874588</v>
       </c>
       <c r="G29">
-        <v>-3.122027674205723</v>
+        <v>-12.07321643565427</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>4.547018605541566</v>
       </c>
       <c r="E30">
-        <v>-30.39004998953945</v>
+        <v>-38.08795540620122</v>
       </c>
       <c r="F30">
-        <v>-4.043164630057226</v>
+        <v>-4.982317283119015</v>
       </c>
       <c r="G30">
-        <v>-4.530065592423005</v>
+        <v>-13.2625266100919</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.456995446785773</v>
       </c>
       <c r="E31">
-        <v>-30.28832234943115</v>
+        <v>-37.65544991067664</v>
       </c>
       <c r="F31">
-        <v>-3.957690438095043</v>
+        <v>-5.098888332583808</v>
       </c>
       <c r="G31">
-        <v>-3.763594846988783</v>
+        <v>-12.76014470341642</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.373444899370598</v>
       </c>
       <c r="E32">
-        <v>-29.52989805110052</v>
+        <v>-35.82128208334991</v>
       </c>
       <c r="F32">
-        <v>-3.942931090816105</v>
+        <v>-4.543443867244266</v>
       </c>
       <c r="G32">
-        <v>-5.280629166541029</v>
+        <v>-12.23598271763808</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.307770964466582</v>
       </c>
       <c r="E33">
-        <v>-29.86625272225724</v>
+        <v>-36.98399042718931</v>
       </c>
       <c r="F33">
-        <v>-4.062730524789522</v>
+        <v>-5.679037818351248</v>
       </c>
       <c r="G33">
-        <v>-4.334571257237963</v>
+        <v>-13.03393344060523</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.274975961591871</v>
       </c>
       <c r="E34">
-        <v>-29.06001679535364</v>
+        <v>-35.0702459903628</v>
       </c>
       <c r="F34">
-        <v>-3.901334263094131</v>
+        <v>-5.033050510267159</v>
       </c>
       <c r="G34">
-        <v>-4.184904803953052</v>
+        <v>-12.6902921925378</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.288081799929069</v>
       </c>
       <c r="E35">
-        <v>-29.04802992465533</v>
+        <v>-36.13740579687736</v>
       </c>
       <c r="F35">
-        <v>-4.287329322158271</v>
+        <v>-4.943763546313557</v>
       </c>
       <c r="G35">
-        <v>-5.743698344937665</v>
+        <v>-14.51878429169745</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.351767495918562</v>
       </c>
       <c r="E36">
-        <v>-28.29009470151754</v>
+        <v>-36.43319666211038</v>
       </c>
       <c r="F36">
-        <v>-3.904032106121082</v>
+        <v>-5.038050269842202</v>
       </c>
       <c r="G36">
-        <v>-5.207982555227263</v>
+        <v>-12.94747192275608</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.465672073454892</v>
       </c>
       <c r="E37">
-        <v>-27.52712381528321</v>
+        <v>-36.89853812266457</v>
       </c>
       <c r="F37">
-        <v>-4.189908444622972</v>
+        <v>-4.880354337018234</v>
       </c>
       <c r="G37">
-        <v>-4.004043080051589</v>
+        <v>-12.87618594565896</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.633471465283121</v>
       </c>
       <c r="E38">
-        <v>-27.27087558508518</v>
+        <v>-35.56690411291704</v>
       </c>
       <c r="F38">
-        <v>-4.134352832962314</v>
+        <v>-4.676163174075838</v>
       </c>
       <c r="G38">
-        <v>-4.02693219191011</v>
+        <v>-13.13146211219216</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>4.849496510723393</v>
       </c>
       <c r="E39">
-        <v>-26.42594384778603</v>
+        <v>-35.58210393592379</v>
       </c>
       <c r="F39">
-        <v>-3.823940930565478</v>
+        <v>-4.508151772771655</v>
       </c>
       <c r="G39">
-        <v>-3.468598755075406</v>
+        <v>-14.07004149912201</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.097501655106447</v>
       </c>
       <c r="E40">
-        <v>-26.67791719852082</v>
+        <v>-35.39506890245899</v>
       </c>
       <c r="F40">
-        <v>-3.980611413809199</v>
+        <v>-4.804715750643889</v>
       </c>
       <c r="G40">
-        <v>-4.181170508584754</v>
+        <v>-13.53352621266387</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.370553425400709</v>
       </c>
       <c r="E41">
-        <v>-26.01445952860505</v>
+        <v>-34.20573765992849</v>
       </c>
       <c r="F41">
-        <v>-4.101085506502593</v>
+        <v>-4.39149124392264</v>
       </c>
       <c r="G41">
-        <v>-4.817927458699253</v>
+        <v>-14.1155283948316</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.655258929349104</v>
       </c>
       <c r="E42">
-        <v>-25.60884411173802</v>
+        <v>-33.56633297970446</v>
       </c>
       <c r="F42">
-        <v>-3.919265773321694</v>
+        <v>-4.295207467234626</v>
       </c>
       <c r="G42">
-        <v>-3.396243471769095</v>
+        <v>-12.8164968095859</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.932369543046525</v>
       </c>
       <c r="E43">
-        <v>-25.43121471878715</v>
+        <v>-34.07958116678581</v>
       </c>
       <c r="F43">
-        <v>-3.562280247363615</v>
+        <v>-3.804203995594314</v>
       </c>
       <c r="G43">
-        <v>-4.28884269170401</v>
+        <v>-13.38613575943721</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.188118063507225</v>
       </c>
       <c r="E44">
-        <v>-23.72128557586086</v>
+        <v>-34.12490892736558</v>
       </c>
       <c r="F44">
-        <v>-3.506336627753674</v>
+        <v>-4.931462110615381</v>
       </c>
       <c r="G44">
-        <v>-4.609925882466844</v>
+        <v>-14.23111609233525</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.413071930710552</v>
       </c>
       <c r="E45">
-        <v>-23.24382591886214</v>
+        <v>-33.68233436988495</v>
       </c>
       <c r="F45">
-        <v>-4.134481113141464</v>
+        <v>-4.501215140862031</v>
       </c>
       <c r="G45">
-        <v>-5.671833022371167</v>
+        <v>-14.32281985904583</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.595438814423086</v>
       </c>
       <c r="E46">
-        <v>-23.63994965420909</v>
+        <v>-32.77374587345997</v>
       </c>
       <c r="F46">
-        <v>-3.501693993862563</v>
+        <v>-4.555301073433161</v>
       </c>
       <c r="G46">
-        <v>-3.936921769242865</v>
+        <v>-13.08362803969523</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.723846643772436</v>
       </c>
       <c r="E47">
-        <v>-22.42850587309914</v>
+        <v>-32.94856308405208</v>
       </c>
       <c r="F47">
-        <v>-3.871718170622455</v>
+        <v>-4.727559974002552</v>
       </c>
       <c r="G47">
-        <v>-5.481731565869597</v>
+        <v>-14.39160306371527</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>6.799524028722483</v>
       </c>
       <c r="E48">
-        <v>-23.29176887318134</v>
+        <v>-33.07715816044789</v>
       </c>
       <c r="F48">
-        <v>-3.531539723691977</v>
+        <v>-3.991152560382364</v>
       </c>
       <c r="G48">
-        <v>-4.396746613011016</v>
+        <v>-14.37882932375199</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.821735333759948</v>
       </c>
       <c r="E49">
-        <v>-22.36605821653337</v>
+        <v>-32.01415775730938</v>
       </c>
       <c r="F49">
-        <v>-3.721715089282735</v>
+        <v>-4.194157527594096</v>
       </c>
       <c r="G49">
-        <v>-4.711526525067077</v>
+        <v>-13.81956065780244</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.786713551029679</v>
       </c>
       <c r="E50">
-        <v>-21.89563127966856</v>
+        <v>-32.10962931057609</v>
       </c>
       <c r="F50">
-        <v>-3.378244909607016</v>
+        <v>-4.372379080935116</v>
       </c>
       <c r="G50">
-        <v>-5.880986668451241</v>
+        <v>-13.07853311011029</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>6.703387662359989</v>
       </c>
       <c r="E51">
-        <v>-21.71686523974176</v>
+        <v>-29.94141633383656</v>
       </c>
       <c r="F51">
-        <v>-3.412121962844181</v>
+        <v>-4.184365473918934</v>
       </c>
       <c r="G51">
-        <v>-5.693613101474032</v>
+        <v>-13.43721747710816</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>6.578645951524535</v>
       </c>
       <c r="E52">
-        <v>-21.69456703372799</v>
+        <v>-29.23656841149068</v>
       </c>
       <c r="F52">
-        <v>-3.528391316332084</v>
+        <v>-4.502809140865921</v>
       </c>
       <c r="G52">
-        <v>-5.457584446706153</v>
+        <v>-13.75708073183978</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>6.416060636961508</v>
       </c>
       <c r="E53">
-        <v>-20.47008577594996</v>
+        <v>-29.35872399784759</v>
       </c>
       <c r="F53">
-        <v>-3.961540427175477</v>
+        <v>-4.727686670475787</v>
       </c>
       <c r="G53">
-        <v>-5.27422326092254</v>
+        <v>-14.01988011311097</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.224112770049995</v>
       </c>
       <c r="E54">
-        <v>-20.43122694049014</v>
+        <v>-28.99767329369004</v>
       </c>
       <c r="F54">
-        <v>-3.398688177416466</v>
+        <v>-4.25959071304935</v>
       </c>
       <c r="G54">
-        <v>-6.0818606401376</v>
+        <v>-13.4008279605405</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.014151671444439</v>
       </c>
       <c r="E55">
-        <v>-20.48366214102495</v>
+        <v>-28.4445790638152</v>
       </c>
       <c r="F55">
-        <v>-3.522204569173419</v>
+        <v>-4.704403026106997</v>
       </c>
       <c r="G55">
-        <v>-4.877722532229569</v>
+        <v>-14.02795122313572</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.792589718282726</v>
       </c>
       <c r="E56">
-        <v>-18.32064558820922</v>
+        <v>-27.92925683563835</v>
       </c>
       <c r="F56">
-        <v>-3.630518175995112</v>
+        <v>-4.021356207748667</v>
       </c>
       <c r="G56">
-        <v>-5.948088115986729</v>
+        <v>-13.97971657462853</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>5.562162113593541</v>
       </c>
       <c r="E57">
-        <v>-18.88804979594829</v>
+        <v>-29.03308143195601</v>
       </c>
       <c r="F57">
-        <v>-3.553460589120533</v>
+        <v>-4.813809390010342</v>
       </c>
       <c r="G57">
-        <v>-5.393724023253612</v>
+        <v>-15.00716921183289</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>5.33516875766103</v>
       </c>
       <c r="E58">
-        <v>-17.68515124529082</v>
+        <v>-28.75528219395547</v>
       </c>
       <c r="F58">
-        <v>-3.443332847172704</v>
+        <v>-4.271109006172341</v>
       </c>
       <c r="G58">
-        <v>-6.583116961329728</v>
+        <v>-13.74840875779966</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>5.116369304142968</v>
       </c>
       <c r="E59">
-        <v>-18.46897122585646</v>
+        <v>-27.54914125590851</v>
       </c>
       <c r="F59">
-        <v>-3.716105602930248</v>
+        <v>-4.5865341296445</v>
       </c>
       <c r="G59">
-        <v>-6.329926438486268</v>
+        <v>-15.23817245847216</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>4.904492794367015</v>
       </c>
       <c r="E60">
-        <v>-17.45402246041333</v>
+        <v>-27.3040104293993</v>
       </c>
       <c r="F60">
-        <v>-3.755527210577367</v>
+        <v>-4.338977139472583</v>
       </c>
       <c r="G60">
-        <v>-6.47586190694842</v>
+        <v>-14.56243880045105</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>4.707824350948994</v>
       </c>
       <c r="E61">
-        <v>-17.0834212045736</v>
+        <v>-29.440440311316</v>
       </c>
       <c r="F61">
-        <v>-3.797041685591739</v>
+        <v>-4.733653282512205</v>
       </c>
       <c r="G61">
-        <v>-6.082661792158103</v>
+        <v>-15.18597012113616</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>4.530470972865455</v>
       </c>
       <c r="E62">
-        <v>-17.86038054701762</v>
+        <v>-27.1614314252678</v>
       </c>
       <c r="F62">
-        <v>-3.498944680393361</v>
+        <v>-4.701552355459206</v>
       </c>
       <c r="G62">
-        <v>-7.199305492008735</v>
+        <v>-14.89415711875879</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>4.371917698865031</v>
       </c>
       <c r="E63">
-        <v>-17.27281104452239</v>
+        <v>-26.13578187574455</v>
       </c>
       <c r="F63">
-        <v>-4.010295605635238</v>
+        <v>-5.212281676129273</v>
       </c>
       <c r="G63">
-        <v>-6.430669649791829</v>
+        <v>-15.23236410632351</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>4.234107588426219</v>
       </c>
       <c r="E64">
-        <v>-16.60084890042022</v>
+        <v>-28.55373340129609</v>
       </c>
       <c r="F64">
-        <v>-4.274500512390254</v>
+        <v>-4.753885125581944</v>
       </c>
       <c r="G64">
-        <v>-6.238591797603315</v>
+        <v>-14.38593044393373</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>4.123142728319052</v>
       </c>
       <c r="E65">
-        <v>-16.50180211692445</v>
+        <v>-27.72258181040228</v>
       </c>
       <c r="F65">
-        <v>-3.930160878166959</v>
+        <v>-4.781301450537074</v>
       </c>
       <c r="G65">
-        <v>-6.308434376845319</v>
+        <v>-15.37196981171457</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>4.039890079998712</v>
       </c>
       <c r="E66">
-        <v>-16.59907826708322</v>
+        <v>-28.94696344175215</v>
       </c>
       <c r="F66">
-        <v>-3.6027138430907</v>
+        <v>-5.044082605674111</v>
       </c>
       <c r="G66">
-        <v>-7.353669609413872</v>
+        <v>-15.3306740666577</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>3.980306323952167</v>
       </c>
       <c r="E67">
-        <v>-16.76234334048176</v>
+        <v>-27.71951150502508</v>
       </c>
       <c r="F67">
-        <v>-4.139770690899032</v>
+        <v>-5.277776626115229</v>
       </c>
       <c r="G67">
-        <v>-7.022161510747873</v>
+        <v>-14.81928582084264</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>3.950948428146074</v>
       </c>
       <c r="E68">
-        <v>-17.21402239495482</v>
+        <v>-27.82968022068368</v>
       </c>
       <c r="F68">
-        <v>-4.076645756815531</v>
+        <v>-4.656548976313121</v>
       </c>
       <c r="G68">
-        <v>-6.87727217467613</v>
+        <v>-14.32567023875514</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>3.952005694896335</v>
       </c>
       <c r="E69">
-        <v>-16.12158238229243</v>
+        <v>-28.09969501186504</v>
       </c>
       <c r="F69">
-        <v>-3.695016183107299</v>
+        <v>-4.995158762534356</v>
       </c>
       <c r="G69">
-        <v>-7.057703527657488</v>
+        <v>-15.10419633577062</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>3.978729976267728</v>
       </c>
       <c r="E70">
-        <v>-16.96618354098903</v>
+        <v>-26.69757077571411</v>
       </c>
       <c r="F70">
-        <v>-4.136489252242241</v>
+        <v>-5.200768925976986</v>
       </c>
       <c r="G70">
-        <v>-6.203106059967867</v>
+        <v>-15.27982574244727</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>4.032617636350995</v>
       </c>
       <c r="E71">
-        <v>-16.5531323698014</v>
+        <v>-26.66382911588296</v>
       </c>
       <c r="F71">
-        <v>-3.837898130798246</v>
+        <v>-5.737889122021937</v>
       </c>
       <c r="G71">
-        <v>-6.547151194591086</v>
+        <v>-14.20118213956916</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>4.115236873305586</v>
       </c>
       <c r="E72">
-        <v>-17.36543645187528</v>
+        <v>-27.5941271167007</v>
       </c>
       <c r="F72">
-        <v>-4.254706564006135</v>
+        <v>-4.960417797720318</v>
       </c>
       <c r="G72">
-        <v>-7.881214972733353</v>
+        <v>-15.50194845067744</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>4.223503668509694</v>
       </c>
       <c r="E73">
-        <v>-17.91627097322029</v>
+        <v>-26.5675628154279</v>
       </c>
       <c r="F73">
-        <v>-4.076919737938902</v>
+        <v>-5.190952324860135</v>
       </c>
       <c r="G73">
-        <v>-6.807628228166482</v>
+        <v>-14.93902328717977</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>4.352507146539208</v>
       </c>
       <c r="E74">
-        <v>-17.22430203095223</v>
+        <v>-27.13104989315034</v>
       </c>
       <c r="F74">
-        <v>-4.23337562903108</v>
+        <v>-5.098629396666635</v>
       </c>
       <c r="G74">
-        <v>-7.289590689955739</v>
+        <v>-14.54195314465404</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>4.505364035592463</v>
       </c>
       <c r="E75">
-        <v>-17.15536959960747</v>
+        <v>-27.30362550910865</v>
       </c>
       <c r="F75">
-        <v>-4.56549697211676</v>
+        <v>-5.318888047974122</v>
       </c>
       <c r="G75">
-        <v>-6.696681915508887</v>
+        <v>-14.61949605282039</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>4.679937877950684</v>
       </c>
       <c r="E76">
-        <v>-18.26894852893766</v>
+        <v>-27.17047025938711</v>
       </c>
       <c r="F76">
-        <v>-4.484686002222589</v>
+        <v>-5.141053710729426</v>
       </c>
       <c r="G76">
-        <v>-6.060073939943655</v>
+        <v>-14.04033100817982</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.86718732411857</v>
       </c>
       <c r="E77">
-        <v>-17.95062397704248</v>
+        <v>-28.33028490833561</v>
       </c>
       <c r="F77">
-        <v>-4.638301516755427</v>
+        <v>-4.947643625806384</v>
       </c>
       <c r="G77">
-        <v>-6.057011685319829</v>
+        <v>-14.73901998897023</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>5.068842997323863</v>
       </c>
       <c r="E78">
-        <v>-18.41466123708247</v>
+        <v>-28.5807185779078</v>
       </c>
       <c r="F78">
-        <v>-4.273524949546344</v>
+        <v>-5.586133670086782</v>
       </c>
       <c r="G78">
-        <v>-5.310957074226293</v>
+        <v>-14.33149183308595</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>5.28279492749806</v>
       </c>
       <c r="E79">
-        <v>-18.35751642357967</v>
+        <v>-29.52023881604216</v>
       </c>
       <c r="F79">
-        <v>-4.665648158650278</v>
+        <v>-5.200361913556718</v>
       </c>
       <c r="G79">
-        <v>-6.874256267689854</v>
+        <v>-13.63073210606072</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>5.501808750006151</v>
       </c>
       <c r="E80">
-        <v>-18.82936530128289</v>
+        <v>-27.99082143977263</v>
       </c>
       <c r="F80">
-        <v>-4.61526651421536</v>
+        <v>-5.34538107238055</v>
       </c>
       <c r="G80">
-        <v>-5.419413856638356</v>
+        <v>-14.12170587280788</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>5.722176930615719</v>
       </c>
       <c r="E81">
-        <v>-19.16619319797342</v>
+        <v>-29.50965350804923</v>
       </c>
       <c r="F81">
-        <v>-4.695017984852102</v>
+        <v>-6.083388028975333</v>
       </c>
       <c r="G81">
-        <v>-5.338232658924349</v>
+        <v>-13.82595166596601</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>5.944330237095322</v>
       </c>
       <c r="E82">
-        <v>-21.03704166476227</v>
+        <v>-30.1460127895031</v>
       </c>
       <c r="F82">
-        <v>-4.88282175083449</v>
+        <v>-5.840512473489455</v>
       </c>
       <c r="G82">
-        <v>-6.102184079203185</v>
+        <v>-13.95255685902435</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>6.163759708713081</v>
       </c>
       <c r="E83">
-        <v>-20.56173303291719</v>
+        <v>-32.02846094246261</v>
       </c>
       <c r="F83">
-        <v>-4.876305592845414</v>
+        <v>-5.503544198449573</v>
       </c>
       <c r="G83">
-        <v>-5.204764704963091</v>
+        <v>-13.79654077939512</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>6.371646572052171</v>
       </c>
       <c r="E84">
-        <v>-22.80220007668611</v>
+        <v>-32.39130265809019</v>
       </c>
       <c r="F84">
-        <v>-4.936397730100848</v>
+        <v>-5.327133612822857</v>
       </c>
       <c r="G84">
-        <v>-5.415590176540498</v>
+        <v>-13.37637627118744</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>6.569564951553143</v>
       </c>
       <c r="E85">
-        <v>-22.32690955873706</v>
+        <v>-32.94894574010573</v>
       </c>
       <c r="F85">
-        <v>-4.358782173798111</v>
+        <v>-5.825677900179533</v>
       </c>
       <c r="G85">
-        <v>-5.637605292040641</v>
+        <v>-13.56196379884621</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>6.752509865515055</v>
       </c>
       <c r="E86">
-        <v>-23.67782128233524</v>
+        <v>-32.78699392416942</v>
       </c>
       <c r="F86">
-        <v>-4.964241655653146</v>
+        <v>-5.480446639525846</v>
       </c>
       <c r="G86">
-        <v>-6.28439981623021</v>
+        <v>-13.38903579732961</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>6.908484062085564</v>
       </c>
       <c r="E87">
-        <v>-24.60843174785951</v>
+        <v>-34.54518075035844</v>
       </c>
       <c r="F87">
-        <v>-5.108131632159271</v>
+        <v>-5.683869705099254</v>
       </c>
       <c r="G87">
-        <v>-5.798021086691566</v>
+        <v>-13.95920940028552</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>7.034550639714611</v>
       </c>
       <c r="E88">
-        <v>-25.14628766269854</v>
+        <v>-33.85586549385887</v>
       </c>
       <c r="F88">
-        <v>-4.572774892651163</v>
+        <v>-5.475726404044878</v>
       </c>
       <c r="G88">
-        <v>-5.530581975847083</v>
+        <v>-14.01379201986425</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>7.123543232337863</v>
       </c>
       <c r="E89">
-        <v>-27.1892362556749</v>
+        <v>-36.01357241090061</v>
       </c>
       <c r="F89">
-        <v>-4.58492983555216</v>
+        <v>-5.644412464069038</v>
       </c>
       <c r="G89">
-        <v>-5.1000653917381</v>
+        <v>-13.18340457170332</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>7.162877000534637</v>
       </c>
       <c r="E90">
-        <v>-28.57378548420206</v>
+        <v>-36.25888890484413</v>
       </c>
       <c r="F90">
-        <v>-5.106437858682709</v>
+        <v>-6.0016680118857</v>
       </c>
       <c r="G90">
-        <v>-4.930840235407175</v>
+        <v>-13.88997099560443</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>7.14302594349046</v>
       </c>
       <c r="E91">
-        <v>-29.28820207212614</v>
+        <v>-36.37375364804869</v>
       </c>
       <c r="F91">
-        <v>-5.282648897364078</v>
+        <v>-6.007563357155923</v>
       </c>
       <c r="G91">
-        <v>-5.416616445657672</v>
+        <v>-12.92097762680529</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>7.056818211672585</v>
       </c>
       <c r="E92">
-        <v>-31.0147643000826</v>
+        <v>-38.54025033313931</v>
       </c>
       <c r="F92">
-        <v>-4.755545641234282</v>
+        <v>-5.975247837951381</v>
       </c>
       <c r="G92">
-        <v>-4.614934737867761</v>
+        <v>-13.71053115101209</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.892881668242071</v>
       </c>
       <c r="E93">
-        <v>-33.64445821328479</v>
+        <v>-40.75101738012893</v>
       </c>
       <c r="F93">
-        <v>-5.111264994312968</v>
+        <v>-6.148220989888635</v>
       </c>
       <c r="G93">
-        <v>-6.049572889493088</v>
+        <v>-14.40313203855578</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.639932443511355</v>
       </c>
       <c r="E94">
-        <v>-35.11363103559329</v>
+        <v>-40.69264761440706</v>
       </c>
       <c r="F94">
-        <v>-5.338723964565001</v>
+        <v>-5.83638850328565</v>
       </c>
       <c r="G94">
-        <v>-5.875127002846732</v>
+        <v>-14.30067065411534</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.299071401439198</v>
       </c>
       <c r="E95">
-        <v>-36.83583687155437</v>
+        <v>-40.93012305560629</v>
       </c>
       <c r="F95">
-        <v>-5.551377660066548</v>
+        <v>-6.2692331466668</v>
       </c>
       <c r="G95">
-        <v>-6.496718343845829</v>
+        <v>-13.32446360658613</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>5.860370066267008</v>
       </c>
       <c r="E96">
-        <v>-38.74394335824133</v>
+        <v>-46.6892234602831</v>
       </c>
       <c r="F96">
-        <v>-5.51325469127009</v>
+        <v>-6.08635114274312</v>
       </c>
       <c r="G96">
-        <v>-7.325771642154433</v>
+        <v>-13.45462101500811</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.32977460436476</v>
       </c>
       <c r="E97">
-        <v>-40.22286824932534</v>
+        <v>-45.76418528202526</v>
       </c>
       <c r="F97">
-        <v>-5.171997740611197</v>
+        <v>-6.181016767912034</v>
       </c>
       <c r="G97">
-        <v>-5.909987047375257</v>
+        <v>-13.84077794416363</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.696977496055105</v>
       </c>
       <c r="E98">
-        <v>-43.13960854445173</v>
+        <v>-48.4805202241792</v>
       </c>
       <c r="F98">
-        <v>-5.5027776847865</v>
+        <v>-6.18821352351827</v>
       </c>
       <c r="G98">
-        <v>-6.99759726284648</v>
+        <v>-14.8324419288157</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.99780134157405</v>
       </c>
       <c r="E99">
-        <v>-44.36545060866907</v>
+        <v>-48.95214947089305</v>
       </c>
       <c r="F99">
-        <v>-5.342208117578967</v>
+        <v>-5.778871471848721</v>
       </c>
       <c r="G99">
-        <v>-6.660454615672642</v>
+        <v>-15.00619425617158</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.194993328107237</v>
       </c>
       <c r="E100">
-        <v>-47.26480156360601</v>
+        <v>-50.80237073857697</v>
       </c>
       <c r="F100">
-        <v>-5.442384643407132</v>
+        <v>-6.366670257187733</v>
       </c>
       <c r="G100">
-        <v>-7.045441266980028</v>
+        <v>-14.99397834313167</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.374744629825341</v>
       </c>
       <c r="E101">
-        <v>-48.59392453451629</v>
+        <v>-52.2367886549951</v>
       </c>
       <c r="F101">
-        <v>-5.510980489575519</v>
+        <v>-6.438137362180812</v>
       </c>
       <c r="G101">
-        <v>-7.663251964973278</v>
+        <v>-14.93183609281401</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.436028390770814</v>
       </c>
       <c r="E102">
-        <v>-51.16424675712242</v>
+        <v>-54.06237275984028</v>
       </c>
       <c r="F102">
-        <v>-5.756427191615113</v>
+        <v>-6.32198916219544</v>
       </c>
       <c r="G102">
-        <v>-8.890577133838363</v>
+        <v>-14.49402803215478</v>
       </c>
     </row>
   </sheetData>
